--- a/parser/data/xlsx/column_inspection.xlsx
+++ b/parser/data/xlsx/column_inspection.xlsx
@@ -5012,35 +5012,35 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>total_eve_charge</t>
+          <t>voice_mail_plan</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>total_day_charge</t>
+          <t>total_intl_charge</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>total_intl_charge</t>
+          <t>total_eve_charge</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>total_night_charge</t>
+          <t>total_day_charge</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>voice_mail_plan</t>
+          <t>total_night_charge</t>
         </is>
       </c>
     </row>

--- a/parser/data/xlsx/column_inspection.xlsx
+++ b/parser/data/xlsx/column_inspection.xlsx
@@ -5012,35 +5012,35 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>voice_mail_plan</t>
+          <t>total_night_charge</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>total_intl_charge</t>
+          <t>total_eve_charge</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>total_eve_charge</t>
+          <t>total_day_charge</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>total_day_charge</t>
+          <t>voice_mail_plan</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>total_night_charge</t>
+          <t>total_intl_charge</t>
         </is>
       </c>
     </row>

--- a/parser/data/xlsx/column_inspection.xlsx
+++ b/parser/data/xlsx/column_inspection.xlsx
@@ -5012,35 +5012,35 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>total_night_charge</t>
+          <t>voice_mail_plan</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>total_eve_charge</t>
+          <t>total_intl_charge</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>total_day_charge</t>
+          <t>total_night_charge</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>voice_mail_plan</t>
+          <t>total_day_charge</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>total_intl_charge</t>
+          <t>total_eve_charge</t>
         </is>
       </c>
     </row>

--- a/parser/data/xlsx/column_inspection.xlsx
+++ b/parser/data/xlsx/column_inspection.xlsx
@@ -423,7 +423,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
-    <col width="95" customWidth="1" min="2" max="2"/>
+    <col width="130" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -434,7 +434,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>data.csv</t>
+          <t>7abc486a8f2944fab510c38389cbf6f4.csv</t>
         </is>
       </c>
     </row>
@@ -446,7 +446,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>C:\Users\Utkarsh Mishra\Downloads\Main Projects\Agentic_Auto_ML\uploaded_files\churn\data.csv</t>
+          <t>C:\Users\Utkarsh Mishra\Downloads\Main Projects\Agentic_Auto_ML\uploaded_files\user_uploads\7abc486a8f2944fab510c38389cbf6f4.csv</t>
         </is>
       </c>
     </row>
@@ -1914,7 +1914,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>str</t>
+          <t>object</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1958,7 +1958,11 @@
         <v>0</v>
       </c>
       <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
       <c r="O21" t="n">
         <v>0.8586</v>
       </c>
@@ -5012,35 +5016,35 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>voice_mail_plan</t>
+          <t>total_day_charge</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>total_intl_charge</t>
+          <t>total_night_charge</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>total_night_charge</t>
+          <t>total_intl_charge</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>total_day_charge</t>
+          <t>total_eve_charge</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>total_eve_charge</t>
+          <t>voice_mail_plan</t>
         </is>
       </c>
     </row>

--- a/parser/data/xlsx/column_inspection.xlsx
+++ b/parser/data/xlsx/column_inspection.xlsx
@@ -434,7 +434,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>7abc486a8f2944fab510c38389cbf6f4.csv</t>
+          <t>5a6b5300428640cbaae38090de224504.csv</t>
         </is>
       </c>
     </row>
@@ -446,7 +446,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>C:\Users\Utkarsh Mishra\Downloads\Main Projects\Agentic_Auto_ML\uploaded_files\user_uploads\7abc486a8f2944fab510c38389cbf6f4.csv</t>
+          <t>C:\Users\Utkarsh Mishra\Downloads\Main Projects\Agentic_Auto_ML\uploaded_files\user_uploads\5a6b5300428640cbaae38090de224504.csv</t>
         </is>
       </c>
     </row>

--- a/parser/data/xlsx/column_inspection.xlsx
+++ b/parser/data/xlsx/column_inspection.xlsx
@@ -14,6 +14,12 @@
     <sheet name="rec_1_derived_relationships" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="rec_1_dependency_graph" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="rec_1_drop_recommendations" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="rec_2_metadata" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="rec_2_column_profiles" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="rec_2_correlation_pairs" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="rec_3_metadata" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="rec_3_column_profiles" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="rec_3_correlation_pairs" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -455,6 +461,2414 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>col_1</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>col_2</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>correlation</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Unnamed:_0</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>latitude</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>-0.008404324847340671</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Unnamed:_0</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>longitude</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>0.009028118267081517</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Unnamed:_0</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>year</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>0.006192532173588739</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>latitude</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>longitude</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>-0.6816971426601179</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>latitude</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>year</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>0.01542487748032483</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>longitude</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>year</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>-0.01193643978508571</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="19" customWidth="1" min="1" max="1"/>
+    <col width="130" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>dataset_file_name</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>42d1e5bfc1a9434c8980fd2b57f3f8d8.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>dataset_file_path</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>C:\Users\Utkarsh Mishra\Downloads\Main Projects\Agentic_Auto_ML\uploaded_files\user_uploads\42d1e5bfc1a9434c8980fd2b57f3f8d8.csv</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:T29"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="19" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="17" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="19" customWidth="1" min="11" max="11"/>
+    <col width="16" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="17" customWidth="1" min="14" max="14"/>
+    <col width="20" customWidth="1" min="15" max="15"/>
+    <col width="22" customWidth="1" min="16" max="16"/>
+    <col width="16" customWidth="1" min="17" max="17"/>
+    <col width="15" customWidth="1" min="18" max="18"/>
+    <col width="20" customWidth="1" min="19" max="19"/>
+    <col width="13" customWidth="1" min="20" max="20"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>column_name</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>technical_type</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>semantic_type</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>role</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>cardinality_level</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>missing_pct</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>missing_pattern</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>distribution_shape</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>outliers_present</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>unique_ratio</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>encoding_required</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>time_dependent</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>unit_scale</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>text_complexity</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>category_imbalance</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>correlation_strength</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>transform_hint</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>modeling_hint</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>data_quality_flags</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>is_constant</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Unnamed:_0</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>int64</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>identifier</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>feature</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>very_high</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>symmetric</t>
+        </is>
+      </c>
+      <c r="I2" t="b">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K2" t="b">
+        <v>0</v>
+      </c>
+      <c r="L2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="n">
+        <v>0.009028118267081517</v>
+      </c>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>datetime</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>feature</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I3" t="b">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.01647</v>
+      </c>
+      <c r="K3" t="b">
+        <v>0</v>
+      </c>
+      <c r="L3" t="b">
+        <v>1</v>
+      </c>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>time</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>datetime</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>feature</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.0144</v>
+      </c>
+      <c r="K4" t="b">
+        <v>0</v>
+      </c>
+      <c r="L4" t="b">
+        <v>1</v>
+      </c>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>text_freeform</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>feature</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I5" t="b">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.02808</v>
+      </c>
+      <c r="K5" t="b">
+        <v>1</v>
+      </c>
+      <c r="L5" t="b">
+        <v>0</v>
+      </c>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>nlp</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>text_freeform</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>feature</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I6" t="b">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.30652</v>
+      </c>
+      <c r="K6" t="b">
+        <v>1</v>
+      </c>
+      <c r="L6" t="b">
+        <v>0</v>
+      </c>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>nlp</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>latitude</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>float64</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>numeric_continuous</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>feature</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>skewed</t>
+        </is>
+      </c>
+      <c r="I7" t="b">
+        <v>1</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.46805</v>
+      </c>
+      <c r="K7" t="b">
+        <v>0</v>
+      </c>
+      <c r="L7" t="b">
+        <v>0</v>
+      </c>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="n">
+        <v>0.6816971426601179</v>
+      </c>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>scaling</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>longitude</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>float64</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>numeric_continuous</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>feature</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>symmetric</t>
+        </is>
+      </c>
+      <c r="I8" t="b">
+        <v>1</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.4807</v>
+      </c>
+      <c r="K8" t="b">
+        <v>0</v>
+      </c>
+      <c r="L8" t="b">
+        <v>0</v>
+      </c>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="n">
+        <v>0.6816971426601179</v>
+      </c>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>scaling</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr"/>
+      <c r="T8" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>accident</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>categorical_nominal</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>feature</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I9" t="b">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="K9" t="b">
+        <v>1</v>
+      </c>
+      <c r="L9" t="b">
+        <v>0</v>
+      </c>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="O9" t="n">
+        <v>1</v>
+      </c>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>encoding</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr"/>
+      <c r="T9" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>belts</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>categorical_nominal</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>feature</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I10" t="b">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
+        <v>2e-05</v>
+      </c>
+      <c r="K10" t="b">
+        <v>1</v>
+      </c>
+      <c r="L10" t="b">
+        <v>0</v>
+      </c>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="O10" t="n">
+        <v>0.97467</v>
+      </c>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>encoding</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr"/>
+      <c r="T10" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>personal_injury</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>categorical_nominal</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>feature</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I11" t="b">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
+        <v>2e-05</v>
+      </c>
+      <c r="K11" t="b">
+        <v>1</v>
+      </c>
+      <c r="L11" t="b">
+        <v>0</v>
+      </c>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="O11" t="n">
+        <v>0.97733</v>
+      </c>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>encoding</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr"/>
+      <c r="T11" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>property_damage</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>categorical_nominal</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>feature</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I12" t="b">
+        <v>0</v>
+      </c>
+      <c r="J12" t="n">
+        <v>2e-05</v>
+      </c>
+      <c r="K12" t="b">
+        <v>1</v>
+      </c>
+      <c r="L12" t="b">
+        <v>0</v>
+      </c>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="O12" t="n">
+        <v>0.96637</v>
+      </c>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>encoding</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr"/>
+      <c r="T12" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>fatal</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>categorical_ordinal</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>feature</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I13" t="b">
+        <v>0</v>
+      </c>
+      <c r="J13" t="n">
+        <v>2e-05</v>
+      </c>
+      <c r="K13" t="b">
+        <v>1</v>
+      </c>
+      <c r="L13" t="b">
+        <v>0</v>
+      </c>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="O13" t="n">
+        <v>0.99965</v>
+      </c>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>encoding</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr"/>
+      <c r="T13" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>commercial_license</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>categorical_nominal</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>feature</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I14" t="b">
+        <v>0</v>
+      </c>
+      <c r="J14" t="n">
+        <v>2e-05</v>
+      </c>
+      <c r="K14" t="b">
+        <v>1</v>
+      </c>
+      <c r="L14" t="b">
+        <v>0</v>
+      </c>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="O14" t="n">
+        <v>0.96982</v>
+      </c>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>encoding</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr"/>
+      <c r="T14" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>hazmat</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>categorical_nominal</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>feature</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I15" t="b">
+        <v>0</v>
+      </c>
+      <c r="J15" t="n">
+        <v>2e-05</v>
+      </c>
+      <c r="K15" t="b">
+        <v>1</v>
+      </c>
+      <c r="L15" t="b">
+        <v>0</v>
+      </c>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="O15" t="n">
+        <v>0.99996</v>
+      </c>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>encoding</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr"/>
+      <c r="T15" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>commercial_vehicle</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>categorical_nominal</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>feature</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I16" t="b">
+        <v>0</v>
+      </c>
+      <c r="J16" t="n">
+        <v>2e-05</v>
+      </c>
+      <c r="K16" t="b">
+        <v>1</v>
+      </c>
+      <c r="L16" t="b">
+        <v>0</v>
+      </c>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="O16" t="n">
+        <v>0.998</v>
+      </c>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>encoding</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr"/>
+      <c r="T16" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>alcohol</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>categorical_nominal</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>feature</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I17" t="b">
+        <v>0</v>
+      </c>
+      <c r="J17" t="n">
+        <v>2e-05</v>
+      </c>
+      <c r="K17" t="b">
+        <v>1</v>
+      </c>
+      <c r="L17" t="b">
+        <v>0</v>
+      </c>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="O17" t="n">
+        <v>0.99904</v>
+      </c>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>encoding</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr"/>
+      <c r="T17" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>work_zone</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>categorical_nominal</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>feature</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I18" t="b">
+        <v>0</v>
+      </c>
+      <c r="J18" t="n">
+        <v>2e-05</v>
+      </c>
+      <c r="K18" t="b">
+        <v>1</v>
+      </c>
+      <c r="L18" t="b">
+        <v>0</v>
+      </c>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="O18" t="n">
+        <v>0.99981</v>
+      </c>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>encoding</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr"/>
+      <c r="T18" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>vehicletype</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>categorical_ordinal</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>feature</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I19" t="b">
+        <v>0</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0.00023</v>
+      </c>
+      <c r="K19" t="b">
+        <v>1</v>
+      </c>
+      <c r="L19" t="b">
+        <v>0</v>
+      </c>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="O19" t="n">
+        <v>0.90506</v>
+      </c>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>encoding</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr"/>
+      <c r="T19" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>year</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>float64</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>numeric_continuous</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>feature</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>0.00746</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>random</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>skewed</t>
+        </is>
+      </c>
+      <c r="I20" t="b">
+        <v>1</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0.00091</v>
+      </c>
+      <c r="K20" t="b">
+        <v>0</v>
+      </c>
+      <c r="L20" t="b">
+        <v>0</v>
+      </c>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="n">
+        <v>0.01542487748032483</v>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>log_candidate</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>scaling</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr"/>
+      <c r="T20" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>make</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>categorical_nominal</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>feature</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I21" t="b">
+        <v>0</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0.00752</v>
+      </c>
+      <c r="K21" t="b">
+        <v>1</v>
+      </c>
+      <c r="L21" t="b">
+        <v>0</v>
+      </c>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr"/>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>encoding</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr"/>
+      <c r="T21" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>categorical_nominal</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>feature</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>0.00012</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>random</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I22" t="b">
+        <v>0</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0.03497</v>
+      </c>
+      <c r="K22" t="b">
+        <v>1</v>
+      </c>
+      <c r="L22" t="b">
+        <v>0</v>
+      </c>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr"/>
+      <c r="P22" t="inlineStr"/>
+      <c r="Q22" t="inlineStr"/>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>encoding</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr"/>
+      <c r="T22" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>color</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>categorical_nominal</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>feature</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>0.01076</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>MAR</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I23" t="b">
+        <v>0</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0.00026</v>
+      </c>
+      <c r="K23" t="b">
+        <v>1</v>
+      </c>
+      <c r="L23" t="b">
+        <v>0</v>
+      </c>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="O23" t="n">
+        <v>0.2028223686870729</v>
+      </c>
+      <c r="P23" t="inlineStr"/>
+      <c r="Q23" t="inlineStr"/>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>encoding</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr"/>
+      <c r="T23" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>violation_type</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>categorical_nominal</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>feature</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I24" t="b">
+        <v>0</v>
+      </c>
+      <c r="J24" t="n">
+        <v>3e-05</v>
+      </c>
+      <c r="K24" t="b">
+        <v>1</v>
+      </c>
+      <c r="L24" t="b">
+        <v>0</v>
+      </c>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="O24" t="n">
+        <v>0.77473</v>
+      </c>
+      <c r="P24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr"/>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>encoding</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr"/>
+      <c r="T24" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>contributed_to_accident</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>categorical_ordinal</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>feature</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I25" t="b">
+        <v>0</v>
+      </c>
+      <c r="J25" t="n">
+        <v>2e-05</v>
+      </c>
+      <c r="K25" t="b">
+        <v>1</v>
+      </c>
+      <c r="L25" t="b">
+        <v>0</v>
+      </c>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="O25" t="n">
+        <v>0.95527</v>
+      </c>
+      <c r="P25" t="inlineStr"/>
+      <c r="Q25" t="inlineStr"/>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>encoding</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr"/>
+      <c r="T25" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>race</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>categorical_nominal</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>feature</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I26" t="b">
+        <v>0</v>
+      </c>
+      <c r="J26" t="n">
+        <v>6e-05</v>
+      </c>
+      <c r="K26" t="b">
+        <v>1</v>
+      </c>
+      <c r="L26" t="b">
+        <v>0</v>
+      </c>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="O26" t="n">
+        <v>0.33093</v>
+      </c>
+      <c r="P26" t="inlineStr"/>
+      <c r="Q26" t="inlineStr"/>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>encoding</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr"/>
+      <c r="T26" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>gender</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>categorical_nominal</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>feature</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I27" t="b">
+        <v>0</v>
+      </c>
+      <c r="J27" t="n">
+        <v>3e-05</v>
+      </c>
+      <c r="K27" t="b">
+        <v>1</v>
+      </c>
+      <c r="L27" t="b">
+        <v>0</v>
+      </c>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="O27" t="n">
+        <v>0.69774</v>
+      </c>
+      <c r="P27" t="inlineStr"/>
+      <c r="Q27" t="inlineStr"/>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>encoding</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr"/>
+      <c r="T27" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>driver_state</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>categorical_nominal</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>feature</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I28" t="b">
+        <v>0</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0.00056</v>
+      </c>
+      <c r="K28" t="b">
+        <v>1</v>
+      </c>
+      <c r="L28" t="b">
+        <v>0</v>
+      </c>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr"/>
+      <c r="P28" t="inlineStr"/>
+      <c r="Q28" t="inlineStr"/>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>encoding</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr"/>
+      <c r="T28" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>dl_state</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>categorical_nominal</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>feature</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
+        <v>0.00151</v>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>random</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I29" t="b">
+        <v>0</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0.00061</v>
+      </c>
+      <c r="K29" t="b">
+        <v>1</v>
+      </c>
+      <c r="L29" t="b">
+        <v>0</v>
+      </c>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr"/>
+      <c r="P29" t="inlineStr"/>
+      <c r="Q29" t="inlineStr"/>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>encoding</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr"/>
+      <c r="T29" t="b">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>col_1</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>col_2</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>correlation</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Unnamed:_0</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>latitude</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>-0.008404324847340671</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Unnamed:_0</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>longitude</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>0.009028118267081517</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Unnamed:_0</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>year</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>0.006192532173588739</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>latitude</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>longitude</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>-0.6816971426601179</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>latitude</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>year</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>0.01542487748032483</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>longitude</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>year</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>-0.01193643978508571</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -5051,4 +7465,2160 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="19" customWidth="1" min="1" max="1"/>
+    <col width="113" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>dataset_file_name</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>data.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>dataset_file_path</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>C:\Users\Utkarsh Mishra\Downloads\Main Projects\Agentic_Auto_ML\uploaded_files\traffic_violations_100k\data.csv</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:T29"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="19" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="17" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="19" customWidth="1" min="11" max="11"/>
+    <col width="16" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="17" customWidth="1" min="14" max="14"/>
+    <col width="20" customWidth="1" min="15" max="15"/>
+    <col width="22" customWidth="1" min="16" max="16"/>
+    <col width="16" customWidth="1" min="17" max="17"/>
+    <col width="15" customWidth="1" min="18" max="18"/>
+    <col width="20" customWidth="1" min="19" max="19"/>
+    <col width="13" customWidth="1" min="20" max="20"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>column_name</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>technical_type</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>semantic_type</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>role</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>cardinality_level</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>missing_pct</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>missing_pattern</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>distribution_shape</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>outliers_present</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>unique_ratio</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>encoding_required</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>time_dependent</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>unit_scale</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>text_complexity</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>category_imbalance</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>correlation_strength</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>transform_hint</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>modeling_hint</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>data_quality_flags</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>is_constant</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Unnamed:_0</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>int64</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>identifier</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>feature</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>very_high</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>symmetric</t>
+        </is>
+      </c>
+      <c r="I2" t="b">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K2" t="b">
+        <v>0</v>
+      </c>
+      <c r="L2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="n">
+        <v>0.009028118267081517</v>
+      </c>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>datetime</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>feature</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I3" t="b">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.01647</v>
+      </c>
+      <c r="K3" t="b">
+        <v>0</v>
+      </c>
+      <c r="L3" t="b">
+        <v>1</v>
+      </c>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>time</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>datetime</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>feature</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.0144</v>
+      </c>
+      <c r="K4" t="b">
+        <v>0</v>
+      </c>
+      <c r="L4" t="b">
+        <v>1</v>
+      </c>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>text_freeform</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>feature</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I5" t="b">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.02808</v>
+      </c>
+      <c r="K5" t="b">
+        <v>1</v>
+      </c>
+      <c r="L5" t="b">
+        <v>0</v>
+      </c>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>nlp</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>text_freeform</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>feature</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I6" t="b">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.30652</v>
+      </c>
+      <c r="K6" t="b">
+        <v>1</v>
+      </c>
+      <c r="L6" t="b">
+        <v>0</v>
+      </c>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>nlp</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>latitude</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>float64</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>numeric_continuous</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>feature</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>skewed</t>
+        </is>
+      </c>
+      <c r="I7" t="b">
+        <v>1</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.46805</v>
+      </c>
+      <c r="K7" t="b">
+        <v>0</v>
+      </c>
+      <c r="L7" t="b">
+        <v>0</v>
+      </c>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="n">
+        <v>0.6816971426601179</v>
+      </c>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>scaling</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>longitude</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>float64</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>numeric_continuous</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>feature</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>symmetric</t>
+        </is>
+      </c>
+      <c r="I8" t="b">
+        <v>1</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.4807</v>
+      </c>
+      <c r="K8" t="b">
+        <v>0</v>
+      </c>
+      <c r="L8" t="b">
+        <v>0</v>
+      </c>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="n">
+        <v>0.6816971426601179</v>
+      </c>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>scaling</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr"/>
+      <c r="T8" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>accident</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>categorical_nominal</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>feature</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I9" t="b">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="K9" t="b">
+        <v>1</v>
+      </c>
+      <c r="L9" t="b">
+        <v>0</v>
+      </c>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="O9" t="n">
+        <v>1</v>
+      </c>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>encoding</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr"/>
+      <c r="T9" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>belts</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>categorical_nominal</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>feature</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I10" t="b">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
+        <v>2e-05</v>
+      </c>
+      <c r="K10" t="b">
+        <v>1</v>
+      </c>
+      <c r="L10" t="b">
+        <v>0</v>
+      </c>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="O10" t="n">
+        <v>0.97467</v>
+      </c>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>encoding</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr"/>
+      <c r="T10" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>personal_injury</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>categorical_nominal</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>feature</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I11" t="b">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
+        <v>2e-05</v>
+      </c>
+      <c r="K11" t="b">
+        <v>1</v>
+      </c>
+      <c r="L11" t="b">
+        <v>0</v>
+      </c>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="O11" t="n">
+        <v>0.97733</v>
+      </c>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>encoding</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr"/>
+      <c r="T11" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>property_damage</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>categorical_ordinal</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>feature</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I12" t="b">
+        <v>0</v>
+      </c>
+      <c r="J12" t="n">
+        <v>2e-05</v>
+      </c>
+      <c r="K12" t="b">
+        <v>1</v>
+      </c>
+      <c r="L12" t="b">
+        <v>0</v>
+      </c>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="O12" t="n">
+        <v>0.96637</v>
+      </c>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>encoding</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr"/>
+      <c r="T12" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>fatal</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>categorical_ordinal</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>feature</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I13" t="b">
+        <v>0</v>
+      </c>
+      <c r="J13" t="n">
+        <v>2e-05</v>
+      </c>
+      <c r="K13" t="b">
+        <v>1</v>
+      </c>
+      <c r="L13" t="b">
+        <v>0</v>
+      </c>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="O13" t="n">
+        <v>0.99965</v>
+      </c>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>encoding</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr"/>
+      <c r="T13" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>commercial_license</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>categorical_nominal</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>feature</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I14" t="b">
+        <v>0</v>
+      </c>
+      <c r="J14" t="n">
+        <v>2e-05</v>
+      </c>
+      <c r="K14" t="b">
+        <v>1</v>
+      </c>
+      <c r="L14" t="b">
+        <v>0</v>
+      </c>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="O14" t="n">
+        <v>0.96982</v>
+      </c>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>encoding</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr"/>
+      <c r="T14" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>hazmat</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>categorical_nominal</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>feature</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I15" t="b">
+        <v>0</v>
+      </c>
+      <c r="J15" t="n">
+        <v>2e-05</v>
+      </c>
+      <c r="K15" t="b">
+        <v>1</v>
+      </c>
+      <c r="L15" t="b">
+        <v>0</v>
+      </c>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="O15" t="n">
+        <v>0.99996</v>
+      </c>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>encoding</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr"/>
+      <c r="T15" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>commercial_vehicle</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>categorical_nominal</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>feature</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I16" t="b">
+        <v>0</v>
+      </c>
+      <c r="J16" t="n">
+        <v>2e-05</v>
+      </c>
+      <c r="K16" t="b">
+        <v>1</v>
+      </c>
+      <c r="L16" t="b">
+        <v>0</v>
+      </c>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="O16" t="n">
+        <v>0.998</v>
+      </c>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>encoding</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr"/>
+      <c r="T16" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>alcohol</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>categorical_nominal</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>feature</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I17" t="b">
+        <v>0</v>
+      </c>
+      <c r="J17" t="n">
+        <v>2e-05</v>
+      </c>
+      <c r="K17" t="b">
+        <v>1</v>
+      </c>
+      <c r="L17" t="b">
+        <v>0</v>
+      </c>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="O17" t="n">
+        <v>0.99904</v>
+      </c>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>encoding</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr"/>
+      <c r="T17" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>work_zone</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>categorical_nominal</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>feature</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I18" t="b">
+        <v>0</v>
+      </c>
+      <c r="J18" t="n">
+        <v>2e-05</v>
+      </c>
+      <c r="K18" t="b">
+        <v>1</v>
+      </c>
+      <c r="L18" t="b">
+        <v>0</v>
+      </c>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="O18" t="n">
+        <v>0.99981</v>
+      </c>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>encoding</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr"/>
+      <c r="T18" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>vehicletype</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>categorical_ordinal</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>feature</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I19" t="b">
+        <v>0</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0.00023</v>
+      </c>
+      <c r="K19" t="b">
+        <v>1</v>
+      </c>
+      <c r="L19" t="b">
+        <v>0</v>
+      </c>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="O19" t="n">
+        <v>0.90506</v>
+      </c>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>encoding</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr"/>
+      <c r="T19" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>year</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>float64</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>numeric_continuous</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>feature</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>0.00746</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>random</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>skewed</t>
+        </is>
+      </c>
+      <c r="I20" t="b">
+        <v>1</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0.00091</v>
+      </c>
+      <c r="K20" t="b">
+        <v>0</v>
+      </c>
+      <c r="L20" t="b">
+        <v>0</v>
+      </c>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="n">
+        <v>0.01542487748032483</v>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>log_candidate</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>scaling</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr"/>
+      <c r="T20" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>make</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>categorical_nominal</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>feature</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I21" t="b">
+        <v>0</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0.00752</v>
+      </c>
+      <c r="K21" t="b">
+        <v>1</v>
+      </c>
+      <c r="L21" t="b">
+        <v>0</v>
+      </c>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr"/>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>encoding</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr"/>
+      <c r="T21" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>categorical_nominal</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>feature</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>0.00012</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>random</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I22" t="b">
+        <v>0</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0.03497</v>
+      </c>
+      <c r="K22" t="b">
+        <v>1</v>
+      </c>
+      <c r="L22" t="b">
+        <v>0</v>
+      </c>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr"/>
+      <c r="P22" t="inlineStr"/>
+      <c r="Q22" t="inlineStr"/>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>encoding</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr"/>
+      <c r="T22" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>color</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>categorical_nominal</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>feature</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>0.01076</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>MAR</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I23" t="b">
+        <v>0</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0.00026</v>
+      </c>
+      <c r="K23" t="b">
+        <v>1</v>
+      </c>
+      <c r="L23" t="b">
+        <v>0</v>
+      </c>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="O23" t="n">
+        <v>0.2028223686870729</v>
+      </c>
+      <c r="P23" t="inlineStr"/>
+      <c r="Q23" t="inlineStr"/>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>encoding</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr"/>
+      <c r="T23" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>violation_type</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>categorical_nominal</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>feature</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I24" t="b">
+        <v>0</v>
+      </c>
+      <c r="J24" t="n">
+        <v>3e-05</v>
+      </c>
+      <c r="K24" t="b">
+        <v>1</v>
+      </c>
+      <c r="L24" t="b">
+        <v>0</v>
+      </c>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="O24" t="n">
+        <v>0.77473</v>
+      </c>
+      <c r="P24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr"/>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>encoding</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr"/>
+      <c r="T24" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>contributed_to_accident</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>categorical_ordinal</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>feature</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I25" t="b">
+        <v>0</v>
+      </c>
+      <c r="J25" t="n">
+        <v>2e-05</v>
+      </c>
+      <c r="K25" t="b">
+        <v>1</v>
+      </c>
+      <c r="L25" t="b">
+        <v>0</v>
+      </c>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="O25" t="n">
+        <v>0.95527</v>
+      </c>
+      <c r="P25" t="inlineStr"/>
+      <c r="Q25" t="inlineStr"/>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>encoding</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr"/>
+      <c r="T25" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>race</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>categorical_nominal</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>feature</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I26" t="b">
+        <v>0</v>
+      </c>
+      <c r="J26" t="n">
+        <v>6e-05</v>
+      </c>
+      <c r="K26" t="b">
+        <v>1</v>
+      </c>
+      <c r="L26" t="b">
+        <v>0</v>
+      </c>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="O26" t="n">
+        <v>0.33093</v>
+      </c>
+      <c r="P26" t="inlineStr"/>
+      <c r="Q26" t="inlineStr"/>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>encoding</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr"/>
+      <c r="T26" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>gender</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>categorical_nominal</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>feature</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I27" t="b">
+        <v>0</v>
+      </c>
+      <c r="J27" t="n">
+        <v>3e-05</v>
+      </c>
+      <c r="K27" t="b">
+        <v>1</v>
+      </c>
+      <c r="L27" t="b">
+        <v>0</v>
+      </c>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="O27" t="n">
+        <v>0.69774</v>
+      </c>
+      <c r="P27" t="inlineStr"/>
+      <c r="Q27" t="inlineStr"/>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>encoding</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr"/>
+      <c r="T27" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>driver_state</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>categorical_nominal</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>feature</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I28" t="b">
+        <v>0</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0.00056</v>
+      </c>
+      <c r="K28" t="b">
+        <v>1</v>
+      </c>
+      <c r="L28" t="b">
+        <v>0</v>
+      </c>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr"/>
+      <c r="P28" t="inlineStr"/>
+      <c r="Q28" t="inlineStr"/>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>encoding</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr"/>
+      <c r="T28" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>dl_state</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>categorical_nominal</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>feature</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
+        <v>0.00151</v>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>random</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I29" t="b">
+        <v>0</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0.00061</v>
+      </c>
+      <c r="K29" t="b">
+        <v>1</v>
+      </c>
+      <c r="L29" t="b">
+        <v>0</v>
+      </c>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr"/>
+      <c r="P29" t="inlineStr"/>
+      <c r="Q29" t="inlineStr"/>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>encoding</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr"/>
+      <c r="T29" t="b">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>